--- a/stories/arbres/ATOM-EMO.LEX.005-04.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gaspard construit un puzzle à l'école. Hélène prend la pièce du milieu. Le puzzle se défait. Gaspard sent son visage chaud. Son ventre est dur. Être en colère, ce n'est pas honteux. Gaspard dit : je suis en colère. Il ouvre les doigts. Ses mains restent loin de Hélène. Gaspard fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers la maîtresse. Il souffle trois fois. Puis il va vers un adulte. Il dit : je suis en colère. La maîtresse écoute. Le soir, à la maison, papa range des cartes. Une carte glisse. Gaspard sent encore le ventre dur. Il se souvient. Il dit : je suis en colère. Les mains restent loin. Il s'éloigne vers le canapé. Il souffle. Il va vers papa. Papa est l'adulte. Papa écoute. La colère a un nom. Les mains restent loin.</t>
+          <t>Gaspard construit un puzzle à l'école. Hélène prend la pièce du milieu. Le puzzle se défait. Gaspard sent son visage chaud. Son ventre est dur. Être en colère, ce n'est pas honteux. Je suis en colère. Il ouvre les doigts. Ses mains restent loin de Hélène. Gaspard fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers la maîtresse. Il souffle trois fois. Puis il va vers un adulte. Je suis en colère. La maîtresse écoute. Le soir, à la maison, papa range des cartes. Une carte glisse. Gaspard sent encore le ventre dur. Il se souvient. Je suis en colère. Les mains restent loin. Il s'éloigne vers le canapé. Il souffle. Il va vers papa. Papa est l'adulte. Papa écoute. La colère a un nom. Les mains restent loin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Gaspard construit un puzzle à l'école. Hélène prend la pièce du milieu. Le puzzle se défait. Gaspard sent son visage chaud. Son ventre est dur. Être en colère, ce n'est pas honteux.
+enfant-m|Je suis en colère. Il ouvre les doigts. Ses mains restent loin de Hélène.
+narrateur|Gaspard fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers la maîtresse. Il souffle trois fois. Puis il va vers un adulte.
+narrateur|Je suis en colère.
+narrateur|La maîtresse écoute. Le soir, à la maison, papa range des cartes. Une carte glisse. Gaspard sent encore le ventre dur. Il se souvient.
+narrateur|Je suis en colère.
+narrateur|Les mains restent loin. Il s'éloigne vers le canapé. Il souffle. Il va vers papa. Papa est l'adulte. Papa écoute. La colère a un nom. Les mains restent loin.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1496,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Gaspard est en colère. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Gaspard a nommé sa colère. Mains loin. Il peut s'éloigner. Il va vers un adulte. Il a repris le geste à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1832,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Gaspard s'assoit près de papa. Les cartes restent sur la table.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1999,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.005-04.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Les mains restent loin. Il s'éloigne vers le canapé. Il souffle. Il va vers papa. Papa est l'adulte. Papa écoute. La colère a un nom. Les mains restent loin.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1503,6 +1509,7 @@
           <t>narrateur|Gaspard est en colère. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1681,7 @@
           <t>narrateur|Gaspard a nommé sa colère. Mains loin. Il peut s'éloigner. Il va vers un adulte. Il a repris le geste à la maison.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1845,7 @@
           <t>narrateur|Gaspard s'assoit près de papa. Les cartes restent sur la table.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.005-04.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gaspard nomme sa colère</t>
+          <t>Le puzzle de Raphaël</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,7 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +831,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Raphaël pose un puzzle. Nina prend une pièce. Il nomme sa colère, s'éloigne, rejoint papa. Le soir, une carte glisse. Il reprend le geste.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1185,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gaspard construit un puzzle à l'école. Hélène prend la pièce du milieu. Le puzzle se défait. Gaspard sent son visage chaud. Son ventre est dur. Être en colère, ce n'est pas honteux. Je suis en colère. Il ouvre les doigts. Ses mains restent loin de Hélène. Gaspard fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers la maîtresse. Il souffle trois fois. Puis il va vers un adulte. Je suis en colère. La maîtresse écoute. Le soir, à la maison, papa range des cartes. Une carte glisse. Gaspard sent encore le ventre dur. Il se souvient. Je suis en colère. Les mains restent loin. Il s'éloigne vers le canapé. Il souffle. Il va vers papa. Papa est l'adulte. Papa écoute. La colère a un nom. Les mains restent loin.</t>
+          <t>La vitre de la salle est toute embuée. Un petit rond y est dessiné au doigt. Dedans, ça sent la soupe à la carotte. Un plaid de laine attend sur le fauteuil. Le plaid est beige, un peu rêche. Une boîte de cartes dort sous la table. Le carton sent le papier sec. Raphaël, tes pieds sont au chaud ? Oui, papa. J'ai mes chaussettes épaisses. Le puzzle est sur le tapis. Les pièces brillent un peu. En ce moment, Raphaël pose des pièces. Les pièces sont lisses et un peu froides. Nina est là, près de lui. Le tapis est épais sous les genoux. Le milieu, c'est le toit rouge. Tu y es presque. Nina prend la pièce du milieu. Le puzzle se défait. Les pièces glissent sur le tapis. Raphaël sent son visage chaud. Son ventre est dur. Être en colère, ce n'est pas honteux. Je suis en colère. Il ouvre les doigts. Ses mains restent loin de Nina. Raphaël fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers le canapé. Il souffle trois fois. Puis il va vers papa. Papa est l'adulte près du fauteuil. Papa, je suis en colère. La pièce du milieu est partie. Tu as dit le nom. Tu es en colère. Bravo, Raphaël. Tes mains sont restées loin. Tu t'es éloigné. Tu es venu vers moi. Tu as fait du bon travail. Tu veux souffler encore ? Oui, papa. Raphaël souffle. Son ventre est un peu moins dur. Le plaid reste sur le fauteuil. Plus tard, le soir est doux. La lampe fait un cercle jaune. Papa range des cartes sur la table. Les cartes sont lisses, un peu glissantes. Une carte glisse. Nina la prend. Raphaël sent encore le ventre dur. Son visage redevient chaud. Il se souvient. Je suis en colère. Les mains restent loin. Il s'éloigne vers le canapé. Il souffle. Il va vers papa. Papa est l'adulte. Papa, je suis en colère encore. Tu as repris le geste. Tu as nommé. Même leçon, autre moment. Bravo. Les mains loin. On s'éloigne. On vient vers un adulte. La colère a un nom. Les cartes restent sur la table.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,13 +1325,78 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Gaspard construit un puzzle à l'école. Hélène prend la pièce du milieu. Le puzzle se défait. Gaspard sent son visage chaud. Son ventre est dur. Être en colère, ce n'est pas honteux.
-enfant-m|Je suis en colère. Il ouvre les doigts. Ses mains restent loin de Hélène.
-narrateur|Gaspard fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers la maîtresse. Il souffle trois fois. Puis il va vers un adulte.
-narrateur|Je suis en colère.
-narrateur|La maîtresse écoute. Le soir, à la maison, papa range des cartes. Une carte glisse. Gaspard sent encore le ventre dur. Il se souvient.
-narrateur|Je suis en colère.
-narrateur|Les mains restent loin. Il s'éloigne vers le canapé. Il souffle. Il va vers papa. Papa est l'adulte. Papa écoute. La colère a un nom. Les mains restent loin.</t>
+          <t>narrateur|La vitre de la salle est toute embuée.
+narrateur|Un petit rond y est dessiné au doigt.
+narrateur|Dedans, ça sent la soupe à la carotte.
+narrateur|Un plaid de laine attend sur le fauteuil.
+narrateur|Le plaid est beige, un peu rêche.
+narrateur|Une boîte de cartes dort sous la table.
+narrateur|Le carton sent le papier sec.
+papa|Raphaël, tes pieds sont au chaud ?
+enfant-m|Oui, papa.
+enfant-m|J'ai mes chaussettes épaisses.
+papa|Le puzzle est sur le tapis.
+papa|Les pièces brillent un peu.
+narrateur|En ce moment, Raphaël pose des pièces.
+narrateur|Les pièces sont lisses et un peu froides.
+narrateur|Nina est là, près de lui.
+narrateur|Le tapis est épais sous les genoux.
+enfant-m|Le milieu, c'est le toit rouge.
+papa|Tu y es presque.
+narrateur|Nina prend la pièce du milieu.
+narrateur|Le puzzle se défait.
+narrateur|Les pièces glissent sur le tapis.
+narrateur|Raphaël sent son visage chaud.
+narrateur|Son ventre est dur.
+narrateur|Être en colère, ce n'est pas honteux.
+enfant-m|Je suis en colère.
+narrateur|Il ouvre les doigts.
+narrateur|Ses mains restent loin de Nina.
+narrateur|Raphaël fait un pas en arrière.
+narrateur|Il peut s'éloigner.
+narrateur|Il s'éloigne vers le canapé.
+narrateur|Il souffle trois fois.
+narrateur|Puis il va vers papa.
+narrateur|Papa est l'adulte près du fauteuil.
+enfant-m|Papa, je suis en colère.
+enfant-m|La pièce du milieu est partie.
+papa|Tu as dit le nom.
+papa|Tu es en colère.
+papa|Bravo, Raphaël.
+papa|Tes mains sont restées loin.
+papa|Tu t'es éloigné.
+papa|Tu es venu vers moi.
+papa|Tu as fait du bon travail.
+papa|Tu veux souffler encore ?
+enfant-m|Oui, papa.
+narrateur|Raphaël souffle.
+narrateur|Son ventre est un peu moins dur.
+narrateur|Le plaid reste sur le fauteuil.
+narrateur|Plus tard, le soir est doux.
+narrateur|La lampe fait un cercle jaune.
+narrateur|Papa range des cartes sur la table.
+narrateur|Les cartes sont lisses, un peu glissantes.
+narrateur|Une carte glisse.
+narrateur|Nina la prend.
+narrateur|Raphaël sent encore le ventre dur.
+narrateur|Son visage redevient chaud.
+narrateur|Il se souvient.
+enfant-m|Je suis en colère.
+narrateur|Les mains restent loin.
+narrateur|Il s'éloigne vers le canapé.
+narrateur|Il souffle.
+narrateur|Il va vers papa.
+narrateur|Papa est l'adulte.
+enfant-m|Papa, je suis en colère encore.
+papa|Tu as repris le geste.
+papa|Tu as nommé.
+papa|Même leçon, autre moment.
+papa|Bravo.
+papa|Les mains loin.
+papa|On s'éloigne.
+papa|On vient vers un adulte.
+narrateur|La colère a un nom.
+narrateur|Les cartes restent sur la table.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1346,7 +1424,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Gaspard est en colère. Que fait-il ?</t>
+          <t>Raphaël est en colère. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1506,7 +1584,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Gaspard est en colère. Que fait-il ?</t>
+          <t>narrateur|Raphaël est en colère.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1534,7 +1613,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Gaspard a nommé sa colère. Mains loin. Il peut s'éloigner. Il va vers un adulte. Il a repris le geste à la maison.</t>
+          <t>Raphaël a nommé sa colère. Mains loin. Il peut s'éloigner. Il va vers papa, l'adulte. Il a repris le geste, le soir. Tu as dit : je suis en colère. Bravo, Raphaël. Tu as fait du bon travail. Mes mains étaient loin. Oui. Et tu es venu vers moi. Le plaid est encore sur le fauteuil. La soupe sent encore un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1757,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Gaspard a nommé sa colère. Mains loin. Il peut s'éloigner. Il va vers un adulte. Il a repris le geste à la maison.</t>
+          <t>narrateur|Raphaël a nommé sa colère.
+narrateur|Mains loin.
+narrateur|Il peut s'éloigner.
+narrateur|Il va vers papa, l'adulte.
+narrateur|Il a repris le geste, le soir.
+papa|Tu as dit : je suis en colère.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+enfant-m|Mes mains étaient loin.
+papa|Oui.
+papa|Et tu es venu vers moi.
+narrateur|Le plaid est encore sur le fauteuil.
+narrateur|La soupe sent encore un peu.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1797,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Gaspard s'assoit près de papa. Les cartes restent sur la table.</t>
+          <t>Raphaël s'assoit près de papa. Les cartes restent sur la table. Tu veux ranger la boîte avec moi ? Oui, papa. Le carton sent encore le papier sec. Tu as nommé deux fois. C'est du bon travail. Je suis moins chaud, maintenant. On laisse le puzzle pour demain ? Oui. La vitre n'est plus embuée. Le cercle jaune de la lampe reste.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1933,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Gaspard s'assoit près de papa. Les cartes restent sur la table.</t>
+          <t>narrateur|Raphaël s'assoit près de papa.
+narrateur|Les cartes restent sur la table.
+papa|Tu veux ranger la boîte avec moi ?
+enfant-m|Oui, papa.
+narrateur|Le carton sent encore le papier sec.
+papa|Tu as nommé deux fois.
+papa|C'est du bon travail.
+enfant-m|Je suis moins chaud, maintenant.
+papa|On laisse le puzzle pour demain ?
+enfant-m|Oui.
+narrateur|La vitre n'est plus embuée.
+narrateur|Le cercle jaune de la lampe reste.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1972,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit : je suis en colère. Je me suis éloigné. Je suis allé vers papa. Bravo, Raphaël. Tu as fait du bon travail. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2112,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai dit : je suis en colère.
+enfant-m|Je me suis éloigné.
+enfant-m|Je suis allé vers papa.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2177,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.005-04.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-04.xlsx
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La vitre de la salle est toute embuée. Un petit rond y est dessiné au doigt. Dedans, ça sent la soupe à la carotte. Un plaid de laine attend sur le fauteuil. Le plaid est beige, un peu rêche. Une boîte de cartes dort sous la table. Le carton sent le papier sec. Raphaël, tes pieds sont au chaud ? Oui, papa. J'ai mes chaussettes épaisses. Le puzzle est sur le tapis. Les pièces brillent un peu. En ce moment, Raphaël pose des pièces. Les pièces sont lisses et un peu froides. Nina est là, près de lui. Le tapis est épais sous les genoux. Le milieu, c'est le toit rouge. Tu y es presque. Nina prend la pièce du milieu. Le puzzle se défait. Les pièces glissent sur le tapis. Raphaël sent son visage chaud. Son ventre est dur. Être en colère, ce n'est pas honteux. Je suis en colère. Il ouvre les doigts. Ses mains restent loin de Nina. Raphaël fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers le canapé. Il souffle trois fois. Puis il va vers papa. Papa est l'adulte près du fauteuil. Papa, je suis en colère. La pièce du milieu est partie. Tu as dit le nom. Tu es en colère. Bravo, Raphaël. Tes mains sont restées loin. Tu t'es éloigné. Tu es venu vers moi. Tu as fait du bon travail. Tu veux souffler encore ? Oui, papa. Raphaël souffle. Son ventre est un peu moins dur. Le plaid reste sur le fauteuil. Plus tard, le soir est doux. La lampe fait un cercle jaune. Papa range des cartes sur la table. Les cartes sont lisses, un peu glissantes. Une carte glisse. Nina la prend. Raphaël sent encore le ventre dur. Son visage redevient chaud. Il se souvient. Je suis en colère. Les mains restent loin. Il s'éloigne vers le canapé. Il souffle. Il va vers papa. Papa est l'adulte. Papa, je suis en colère encore. Tu as repris le geste. Tu as nommé. Même leçon, autre moment. Bravo. Les mains loin. On s'éloigne. On vient vers un adulte. La colère a un nom. Les cartes restent sur la table.</t>
+          <t>La vitre de la salle est toute embuée. Un petit rond y est dessiné au doigt. Dedans, ça sent la soupe à la carotte. Un plaid de laine attend sur le fauteuil. Le plaid est beige, un peu rêche. Une boîte de cartes dort sous la table. Le carton sent le papier sec. Raphaël, tes pieds sont au chaud ? Oui, papa. J'ai mes chaussettes épaisses. Le puzzle est sur le tapis. Les pièces brillent un peu. En ce moment, Raphaël pose des pièces. Les pièces sont lisses et un peu froides. Nina est là, près de lui. Le tapis est épais sous les genoux. Le milieu, c'est le toit rouge. Tu y es presque. Nina prend la pièce du milieu. Le puzzle se défait. Les pièces glissent sur le tapis. Raphaël sent son visage chaud. Son ventre est dur. Être en colère, ce n'est pas honteux. Je suis en colère. Il ouvre les doigts. Ses mains restent loin de Nina. Raphaël fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers le canapé. Il souffle trois fois. Puis il va vers papa. Papa est l'adulte près du fauteuil. Papa, je suis en colère. La pièce du milieu est partie. Tu as dit le nom. Tu es en colère. Bravo, Raphaël. Tes mains sont restées loin. Tu t'es éloigné. Tu es venu vers moi. Tu veux souffler encore ? Oui, papa. Raphaël souffle. Son ventre est un peu moins dur. Le plaid reste sur le fauteuil. Plus tard, le soir est doux. La lampe fait un cercle jaune. Papa range des cartes sur la table. Les cartes sont lisses, un peu glissantes. Une carte glisse. Nina la prend. Raphaël sent encore le ventre dur. Son visage redevient chaud. Il se souvient. Je suis en colère. Les mains restent loin. Il s'éloigne vers le canapé. Il souffle. Il va vers papa. Papa est l'adulte. Papa, je suis en colère encore. Tu as repris le geste. Tu as nommé. Même leçon, autre moment. Bravo. Les mains loin. On s'éloigne. On vient vers un adulte. La colère a un nom. Les cartes restent sur la table.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gaspard construit un puzzle à l'école. Hélène prend la pièce du milieu. Le puzzle se défait. Gaspard sent son visage chaud. Son ventre est dur. Être en &lt;emphasis level="moderate"&gt;colère&lt;/emphasis&gt;, ce n'est pas honteux. Gaspard dit : je suis en colère. Il ouvre les doigts. Ses mains restent loin de Hélène. Gaspard fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers la maîtresse. Il souffle trois fois. Puis il va vers un adulte. Il dit : je suis en colère. La maîtresse écoute. Le soir, à la maison, papa range des cartes. Une carte glisse. Gaspard sent encore le ventre dur. Il se souvient. Il dit : je suis en colère. Les mains restent loin. Il s'éloigne vers le canapé. Il souffle. Il va vers papa. Papa est l'adulte. Papa écoute. La colère a un nom. Les mains restent loin.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La vitre de la salle est toute embuée. Un petit rond y est dessiné au doigt. Dedans, ça sent la soupe à la carotte. Un plaid de laine attend sur le fauteuil. Le plaid est beige, un peu rêche. Une boîte de cartes dort sous la table. Le carton sent le papier sec. Raphaël, tes pieds sont au chaud ? Oui, papa. J'ai mes chaussettes épaisses. Le puzzle est sur le tapis. Les pièces brillent un peu. En ce moment, Raphaël pose des pièces. Les pièces sont lisses et un peu froides. Nina est là, près de lui. Le tapis est épais sous les genoux. Le milieu, c'est le toit rouge. Tu y es presque. Nina prend la pièce du milieu. Le puzzle se défait. Les pièces glissent sur le tapis. Raphaël sent son visage chaud. Son ventre est dur. Être en colère, ce n'est pas honteux. Je suis en colère. Il ouvre les doigts. Ses mains restent loin de Nina. Raphaël fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers le canapé. Il souffle trois fois. Puis il va vers papa. Papa est l'adulte près du fauteuil. Papa, je suis en colère. La pièce du milieu est partie. Tu as dit le nom. Tu es en colère. Bravo, Raphaël. Tes mains sont restées loin. Tu t'es éloigné. Tu es venu vers moi. Tu veux souffler encore ? Oui, papa. Raphaël souffle. Son ventre est un peu moins dur. Le plaid reste sur le fauteuil. Plus tard, le soir est doux. La lampe fait un cercle jaune. Papa range des cartes sur la table. Les cartes sont lisses, un peu glissantes. Une carte glisse. Nina la prend. Raphaël sent encore le ventre dur. Son visage redevient chaud. Il se souvient. Je suis en colère. Les mains restent loin. Il s'éloigne vers le canapé. Il souffle. Il va vers papa. Papa est l'adulte. Papa, je suis en colère encore. Tu as repris le geste. Tu as nommé. Même leçon, autre moment. Bravo. Les mains loin. On s'éloigne. On vient vers un adulte. La colère a un nom. Les cartes restent sur la table.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1366,7 +1366,6 @@
 papa|Tes mains sont restées loin.
 papa|Tu t'es éloigné.
 papa|Tu es venu vers moi.
-papa|Tu as fait du bon travail.
 papa|Tu veux souffler encore ?
 enfant-m|Oui, papa.
 narrateur|Raphaël souffle.
@@ -1399,7 +1398,6 @@
 narrateur|Les cartes restent sur la table.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1429,7 +1427,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gaspard est en &lt;emphasis level="moderate"&gt;colère&lt;/emphasis&gt;. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël est en colère. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1588,7 +1586,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1613,12 +1610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a nommé sa colère. Mains loin. Il peut s'éloigner. Il va vers papa, l'adulte. Il a repris le geste, le soir. Tu as dit : je suis en colère. Bravo, Raphaël. Tu as fait du bon travail. Mes mains étaient loin. Oui. Et tu es venu vers moi. Le plaid est encore sur le fauteuil. La soupe sent encore un peu.</t>
+          <t>Raphaël a nommé sa colère. Mains loin. Il peut s'éloigner. Il va vers papa, l'adulte. Il a repris le geste, le soir. Tu as dit : je suis en colère. Bravo, Raphaël. Mes mains étaient loin. Oui. Et tu es venu vers moi. Le plaid est encore sur le fauteuil. La soupe sent encore un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gaspard a nommé sa &lt;emphasis level="moderate"&gt;colère&lt;/emphasis&gt;. Mains loin. Il peut s'éloigner. Il va vers un adulte. Il a repris le geste à la maison.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a nommé sa colère. Mains loin. Il peut s'éloigner. Il va vers papa, l'adulte. Il a repris le geste, le soir. Tu as dit : je suis en colère. Bravo, Raphaël. Mes mains étaient loin. Oui. Et tu es venu vers moi. Le plaid est encore sur le fauteuil. La soupe sent encore un peu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1764,7 +1761,6 @@
 narrateur|Il a repris le geste, le soir.
 papa|Tu as dit : je suis en colère.
 papa|Bravo, Raphaël.
-papa|Tu as fait du bon travail.
 enfant-m|Mes mains étaient loin.
 papa|Oui.
 papa|Et tu es venu vers moi.
@@ -1772,7 +1768,6 @@
 narrateur|La soupe sent encore un peu.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1797,12 +1792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Raphaël s'assoit près de papa. Les cartes restent sur la table. Tu veux ranger la boîte avec moi ? Oui, papa. Le carton sent encore le papier sec. Tu as nommé deux fois. C'est du bon travail. Je suis moins chaud, maintenant. On laisse le puzzle pour demain ? Oui. La vitre n'est plus embuée. Le cercle jaune de la lampe reste.</t>
+          <t>Raphaël s'assoit près de papa. Les cartes restent sur la table. Tu veux ranger la boîte avec moi ? Oui, papa. Le carton sent encore le papier sec. Tu as nommé deux fois. Je suis moins chaud, maintenant. On laisse le puzzle pour demain ? Oui. La vitre n'est plus embuée. Le cercle jaune de la lampe reste.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gaspard s'assoit près de papa. Les cartes restent sur la table.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël s'assoit près de papa. Les cartes restent sur la table. Tu veux ranger la boîte avec moi ? Oui, papa. Le carton sent encore le papier sec. Tu as nommé deux fois. Je suis moins chaud, maintenant. On laisse le puzzle pour demain ? Oui. La vitre n'est plus embuée. Le cercle jaune de la lampe reste.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1939,7 +1934,6 @@
 enfant-m|Oui, papa.
 narrateur|Le carton sent encore le papier sec.
 papa|Tu as nommé deux fois.
-papa|C'est du bon travail.
 enfant-m|Je suis moins chaud, maintenant.
 papa|On laisse le puzzle pour demain ?
 enfant-m|Oui.
@@ -1947,7 +1941,6 @@
 narrateur|Le cercle jaune de la lampe reste.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1972,12 +1965,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit : je suis en colère. Je me suis éloigné. Je suis allé vers papa. Bravo, Raphaël. Tu as fait du bon travail. L'histoire est finie.</t>
+          <t>J'ai dit : je suis en colère. Je me suis éloigné. Je suis allé vers papa. Bravo, Raphaël.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit : je suis en colère. Je me suis éloigné. Je suis allé vers papa. Bravo, Raphaël.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2115,12 +2108,9 @@
           <t>enfant-m|J'ai dit : je suis en colère.
 enfant-m|Je me suis éloigné.
 enfant-m|Je suis allé vers papa.
-papa|Bravo, Raphaël.
-papa|Tu as fait du bon travail.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|Bravo, Raphaël.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2139,7 +2129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2184,6 +2174,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.005-04.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-04.xlsx
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -672,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>école puis maison</t>
+          <t>salon puis table, fin d'après-midi</t>
         </is>
       </c>
     </row>
@@ -684,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gaspard, Hélène, papa</t>
+          <t>Raphaël, Nina, papa</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.005-04.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-04.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Raphaël pose un puzzle. Nina prend une pièce. Il nomme sa colère, s'éloigne, rejoint papa. Le soir, une carte glisse. Il reprend le geste.</t>
+          <t>Raphaël veut le toit rouge du puzzle. Nina prend la pièce. Il dit sa colère, recule, rejoint papa. Le soir, une carte glisse. Il recule encore. Le toit retrouve sa place.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La vitre de la salle est toute embuée. Un petit rond y est dessiné au doigt. Dedans, ça sent la soupe à la carotte. Un plaid de laine attend sur le fauteuil. Le plaid est beige, un peu rêche. Une boîte de cartes dort sous la table. Le carton sent le papier sec. Raphaël, tes pieds sont au chaud ? Oui, papa. J'ai mes chaussettes épaisses. Le puzzle est sur le tapis. Les pièces brillent un peu. En ce moment, Raphaël pose des pièces. Les pièces sont lisses et un peu froides. Nina est là, près de lui. Le tapis est épais sous les genoux. Le milieu, c'est le toit rouge. Tu y es presque. Nina prend la pièce du milieu. Le puzzle se défait. Les pièces glissent sur le tapis. Raphaël sent son visage chaud. Son ventre est dur. Être en colère, ce n'est pas honteux. Je suis en colère. Il ouvre les doigts. Ses mains restent loin de Nina. Raphaël fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers le canapé. Il souffle trois fois. Puis il va vers papa. Papa est l'adulte près du fauteuil. Papa, je suis en colère. La pièce du milieu est partie. Tu as dit le nom. Tu es en colère. Bravo, Raphaël. Tes mains sont restées loin. Tu t'es éloigné. Tu es venu vers moi. Tu veux souffler encore ? Oui, papa. Raphaël souffle. Son ventre est un peu moins dur. Le plaid reste sur le fauteuil. Plus tard, le soir est doux. La lampe fait un cercle jaune. Papa range des cartes sur la table. Les cartes sont lisses, un peu glissantes. Une carte glisse. Nina la prend. Raphaël sent encore le ventre dur. Son visage redevient chaud. Il se souvient. Je suis en colère. Les mains restent loin. Il s'éloigne vers le canapé. Il souffle. Il va vers papa. Papa est l'adulte. Papa, je suis en colère encore. Tu as repris le geste. Tu as nommé. Même leçon, autre moment. Bravo. Les mains loin. On s'éloigne. On vient vers un adulte. La colère a un nom. Les cartes restent sur la table.</t>
+          <t>La vitre de la salle est toute embuée. Un petit rond y est dessiné au doigt. Dedans, ça sent la soupe à la carotte. Un plaid de laine attend sur le fauteuil. Le plaid est beige, un peu rêche. Une boîte de cartes dort sous la table. Le carton sent le papier sec. Raphaël, tes pieds sont au chaud ? Oui, papa. J'ai mes chaussettes épaisses. Le puzzle est sur le tapis. Je veux le toit rouge. Le milieu est encore vide. En ce moment, Raphaël pose des pièces. Les pièces sont lisses et un peu froides. Nina est là, près de lui. Le tapis est épais sous les genoux. Le milieu, c'est le toit rouge. Tu y es presque. Nina prend la pièce du milieu. Le puzzle se défait. Les pièces glissent sur le tapis. Raphaël sent son visage chaud. Son ventre est dur. Je suis en colère. Il ouvre les doigts. Ses mains restent loin de Nina. Il recule d'un pas. Il marche vers le canapé. Le plaid rêche touche son bras. Il souffle trois fois. Puis il va vers papa. Papa, la pièce du milieu est partie. Je t'écoute. Tu veux venir près du plaid ? Oui, papa. Raphaël s'assoit contre le fauteuil. Le ventre se desserre un peu. On reste ici un moment ? Un moment. Nina pose la pièce près de la boîte. Le toit rouge attend, tout seul. Plus tard, la lampe fait un cercle jaune. La table est lisse sous les cartes. Papa glisse une carte dans la boîte. Je veux celle-là, la bleue. Elle est un peu glissante. La carte part sur le bois. Nina la prend. Le visage de Raphaël redevient chaud. Son ventre se durcit. Il ouvre encore les doigts. Il recule vers le fauteuil. Le plaid est tiède, maintenant. Il va près de papa. Nina a pris la carte. Je t'écoute. On s'assoit un peu ? Oui. Raphaël pose les mains sur ses genoux. Les cartes restent sur la table. La soupe sent encore, tu trouves ? Oui. La carotte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>La vitre de la salle est toute embuée. Un petit rond y est dessiné au doigt. Dedans, ça sent la soupe à la carotte. Un plaid de laine attend sur le fauteuil. Le plaid est beige, un peu rêche. Une boîte de cartes dort sous la table. Le carton sent le papier sec. Raphaël, tes pieds sont au chaud ? Oui, papa. J'ai mes chaussettes épaisses. Le puzzle est sur le tapis. Les pièces brillent un peu. En ce moment, Raphaël pose des pièces. Les pièces sont lisses et un peu froides. Nina est là, près de lui. Le tapis est épais sous les genoux. Le milieu, c'est le toit rouge. Tu y es presque. Nina prend la pièce du milieu. Le puzzle se défait. Les pièces glissent sur le tapis. Raphaël sent son visage chaud. Son ventre est dur. Être en colère, ce n'est pas honteux. Je suis en colère. Il ouvre les doigts. Ses mains restent loin de Nina. Raphaël fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers le canapé. Il souffle trois fois. Puis il va vers papa. Papa est l'adulte près du fauteuil. Papa, je suis en colère. La pièce du milieu est partie. Tu as dit le nom. Tu es en colère. Bravo, Raphaël. Tes mains sont restées loin. Tu t'es éloigné. Tu es venu vers moi. Tu veux souffler encore ? Oui, papa. Raphaël souffle. Son ventre est un peu moins dur. Le plaid reste sur le fauteuil. Plus tard, le soir est doux. La lampe fait un cercle jaune. Papa range des cartes sur la table. Les cartes sont lisses, un peu glissantes. Une carte glisse. Nina la prend. Raphaël sent encore le ventre dur. Son visage redevient chaud. Il se souvient. Je suis en colère. Les mains restent loin. Il s'éloigne vers le canapé. Il souffle. Il va vers papa. Papa est l'adulte. Papa, je suis en colère encore. Tu as repris le geste. Tu as nommé. Même leçon, autre moment. Bravo. Les mains loin. On s'éloigne. On vient vers un adulte. La colère a un nom. Les cartes restent sur la table.</t>
+          <t>La vitre de la salle est toute embuée. Un petit rond y est dessiné au doigt. Dedans, ça sent la soupe à la carotte. Un plaid de laine attend sur le fauteuil. Le plaid est beige, un peu rêche. Une boîte de cartes dort sous la table. Le carton sent le papier sec. Raphaël, tes pieds sont au chaud ? Oui, papa. J'ai mes chaussettes épaisses. Le puzzle est sur le tapis. Je veux le toit rouge. Le milieu est encore vide. En ce moment, Raphaël pose des pièces. Les pièces sont lisses et un peu froides. Nina est là, près de lui. Le tapis est épais sous les genoux. Le milieu, c'est le toit rouge. Tu y es presque. Nina prend la pièce du milieu. Le puzzle se défait. Les pièces glissent sur le tapis. Raphaël sent son visage chaud. Son ventre est dur. Je suis en colère. Il ouvre les doigts. Ses mains restent loin de Nina. Il recule d'un pas. Il marche vers le canapé. Le plaid rêche touche son bras. Il souffle trois fois. Puis il va vers papa. Papa, la pièce du milieu est partie. Je t'écoute. Tu veux venir près du plaid ? Oui, papa. Raphaël s'assoit contre le fauteuil. Le ventre se desserre un peu. On reste ici un moment ? Un moment. Nina pose la pièce près de la boîte. Le toit rouge attend, tout seul. Plus tard, la lampe fait un cercle jaune. La table est lisse sous les cartes. Papa glisse une carte dans la boîte. Je veux celle-là, la bleue. Elle est un peu glissante. La carte part sur le bois. Nina la prend. Le visage de Raphaël redevient chaud. Son ventre se durcit. Il ouvre encore les doigts. Il recule vers le fauteuil. Le plaid est tiède, maintenant. Il va près de papa. Nina a pris la carte. Je t'écoute. On s'assoit un peu ? Oui. Raphaël pose les mains sur ses genoux. Les cartes restent sur la table. La soupe sent encore, tu trouves ? Oui. La carotte.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1335,7 +1335,8 @@
 enfant-m|Oui, papa.
 enfant-m|J'ai mes chaussettes épaisses.
 papa|Le puzzle est sur le tapis.
-papa|Les pièces brillent un peu.
+enfant-m|Je veux le toit rouge.
+papa|Le milieu est encore vide.
 narrateur|En ce moment, Raphaël pose des pièces.
 narrateur|Les pièces sont lisses et un peu froides.
 narrateur|Nina est là, près de lui.
@@ -1347,54 +1348,46 @@
 narrateur|Les pièces glissent sur le tapis.
 narrateur|Raphaël sent son visage chaud.
 narrateur|Son ventre est dur.
-narrateur|Être en colère, ce n'est pas honteux.
 enfant-m|Je suis en colère.
 narrateur|Il ouvre les doigts.
 narrateur|Ses mains restent loin de Nina.
-narrateur|Raphaël fait un pas en arrière.
-narrateur|Il peut s'éloigner.
-narrateur|Il s'éloigne vers le canapé.
+narrateur|Il recule d'un pas.
+narrateur|Il marche vers le canapé.
+narrateur|Le plaid rêche touche son bras.
 narrateur|Il souffle trois fois.
 narrateur|Puis il va vers papa.
-narrateur|Papa est l'adulte près du fauteuil.
-enfant-m|Papa, je suis en colère.
-enfant-m|La pièce du milieu est partie.
-papa|Tu as dit le nom.
-papa|Tu es en colère.
-papa|Bravo, Raphaël.
-papa|Tes mains sont restées loin.
-papa|Tu t'es éloigné.
-papa|Tu es venu vers moi.
-papa|Tu veux souffler encore ?
+enfant-m|Papa, la pièce du milieu est partie.
+papa|Je t'écoute.
+papa|Tu veux venir près du plaid ?
 enfant-m|Oui, papa.
-narrateur|Raphaël souffle.
-narrateur|Son ventre est un peu moins dur.
-narrateur|Le plaid reste sur le fauteuil.
-narrateur|Plus tard, le soir est doux.
-narrateur|La lampe fait un cercle jaune.
-narrateur|Papa range des cartes sur la table.
-narrateur|Les cartes sont lisses, un peu glissantes.
-narrateur|Une carte glisse.
+narrateur|Raphaël s'assoit contre le fauteuil.
+narrateur|Le ventre se desserre un peu.
+papa|On reste ici un moment ?
+enfant-m|Un moment.
+narrateur|Nina pose la pièce près de la boîte.
+narrateur|Le toit rouge attend, tout seul.
+narrateur|Plus tard, la lampe fait un cercle jaune.
+narrateur|La table est lisse sous les cartes.
+narrateur|Papa glisse une carte dans la boîte.
+enfant-m|Je veux celle-là, la bleue.
+papa|Elle est un peu glissante.
+narrateur|La carte part sur le bois.
 narrateur|Nina la prend.
-narrateur|Raphaël sent encore le ventre dur.
-narrateur|Son visage redevient chaud.
-narrateur|Il se souvient.
-enfant-m|Je suis en colère.
-narrateur|Les mains restent loin.
-narrateur|Il s'éloigne vers le canapé.
-narrateur|Il souffle.
-narrateur|Il va vers papa.
-narrateur|Papa est l'adulte.
-enfant-m|Papa, je suis en colère encore.
-papa|Tu as repris le geste.
-papa|Tu as nommé.
-papa|Même leçon, autre moment.
-papa|Bravo.
-papa|Les mains loin.
-papa|On s'éloigne.
-papa|On vient vers un adulte.
-narrateur|La colère a un nom.
-narrateur|Les cartes restent sur la table.</t>
+narrateur|Le visage de Raphaël redevient chaud.
+narrateur|Son ventre se durcit.
+narrateur|Il ouvre encore les doigts.
+narrateur|Il recule vers le fauteuil.
+narrateur|Le plaid est tiède, maintenant.
+narrateur|Il va près de papa.
+enfant-m|Nina a pris la carte.
+papa|Je t'écoute.
+papa|On s'assoit un peu ?
+enfant-m|Oui.
+narrateur|Raphaël pose les mains sur ses genoux.
+narrateur|Les cartes restent sur la table.
+papa|La soupe sent encore, tu trouves ?
+enfant-m|Oui.
+enfant-m|La carotte.</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1449,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Gaspard garde les mains loin. Puis il va où ?</t>
+          <t>Raphaël ouvre les doigts. Puis il va où ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1498,14 +1491,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1609,12 +1602,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a nommé sa colère. Mains loin. Il peut s'éloigner. Il va vers papa, l'adulte. Il a repris le geste, le soir. Tu as dit : je suis en colère. Bravo, Raphaël. Mes mains étaient loin. Oui. Et tu es venu vers moi. Le plaid est encore sur le fauteuil. La soupe sent encore un peu.</t>
+          <t>Raphaël revient près du tapis. Les pièces sont froides, encore. On cherche le toit rouge ? Il est près de la boîte. Nina pousse la pièce vers lui. Raphaël la pose au milieu. Le toit retrouve la maison. Bravo, Raphaël. Elle tient. Oui. Le plaid reste sur le fauteuil. La soupe sent encore un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a nommé sa colère. Mains loin. Il peut s'éloigner. Il va vers papa, l'adulte. Il a repris le geste, le soir. Tu as dit : je suis en colère. Bravo, Raphaël. Mes mains étaient loin. Oui. Et tu es venu vers moi. Le plaid est encore sur le fauteuil. La soupe sent encore un peu.</t>
+          <t>Raphaël revient près du tapis. Les pièces sont froides, encore. On cherche le toit rouge ? Il est près de la boîte. Nina pousse la pièce vers lui. Raphaël la pose au milieu. Le toit retrouve la maison. Bravo, Raphaël. Elle tient. Oui. Le plaid reste sur le fauteuil. La soupe sent encore un peu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1677,7 +1670,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1753,17 +1746,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a nommé sa colère.
-narrateur|Mains loin.
-narrateur|Il peut s'éloigner.
-narrateur|Il va vers papa, l'adulte.
-narrateur|Il a repris le geste, le soir.
-papa|Tu as dit : je suis en colère.
+          <t>narrateur|Raphaël revient près du tapis.
+narrateur|Les pièces sont froides, encore.
+papa|On cherche le toit rouge ?
+enfant-m|Il est près de la boîte.
+narrateur|Nina pousse la pièce vers lui.
+narrateur|Raphaël la pose au milieu.
+narrateur|Le toit retrouve la maison.
 papa|Bravo, Raphaël.
-enfant-m|Mes mains étaient loin.
+enfant-m|Elle tient.
 papa|Oui.
-papa|Et tu es venu vers moi.
-narrateur|Le plaid est encore sur le fauteuil.
+narrateur|Le plaid reste sur le fauteuil.
 narrateur|La soupe sent encore un peu.</t>
         </is>
       </c>
@@ -1791,12 +1784,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Raphaël s'assoit près de papa. Les cartes restent sur la table. Tu veux ranger la boîte avec moi ? Oui, papa. Le carton sent encore le papier sec. Tu as nommé deux fois. Je suis moins chaud, maintenant. On laisse le puzzle pour demain ? Oui. La vitre n'est plus embuée. Le cercle jaune de la lampe reste.</t>
+          <t>Raphaël s'assoit près de papa. Les cartes rentrent dans le carton. On pose la boîte sous la table ? Oui, papa. Le carton sent encore le papier sec. Le toit est rouge, maintenant. Il brille un peu. La vitre n'est plus embuée. Le cercle jaune de la lampe reste.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Raphaël s'assoit près de papa. Les cartes restent sur la table. Tu veux ranger la boîte avec moi ? Oui, papa. Le carton sent encore le papier sec. Tu as nommé deux fois. Je suis moins chaud, maintenant. On laisse le puzzle pour demain ? Oui. La vitre n'est plus embuée. Le cercle jaune de la lampe reste.</t>
+          <t>Raphaël s'assoit près de papa. Les cartes rentrent dans le carton. On pose la boîte sous la table ? Oui, papa. Le carton sent encore le papier sec. Le toit est rouge, maintenant. Il brille un peu. La vitre n'est plus embuée. Le cercle jaune de la lampe reste.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1859,7 +1852,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1928,14 +1921,12 @@
       <c r="AW5" t="inlineStr">
         <is>
           <t>narrateur|Raphaël s'assoit près de papa.
-narrateur|Les cartes restent sur la table.
-papa|Tu veux ranger la boîte avec moi ?
+narrateur|Les cartes rentrent dans le carton.
+papa|On pose la boîte sous la table ?
 enfant-m|Oui, papa.
 narrateur|Le carton sent encore le papier sec.
-papa|Tu as nommé deux fois.
-enfant-m|Je suis moins chaud, maintenant.
-papa|On laisse le puzzle pour demain ?
-enfant-m|Oui.
+enfant-m|Le toit est rouge, maintenant.
+papa|Il brille un peu.
 narrateur|La vitre n'est plus embuée.
 narrateur|Le cercle jaune de la lampe reste.</t>
         </is>
@@ -1964,12 +1955,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit : je suis en colère. Je me suis éloigné. Je suis allé vers papa. Bravo, Raphaël.</t>
+          <t>Le puzzle est entier. Merci, Raphaël. Le toit rouge reste au milieu. La soupe fume encore, tout doux.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit : je suis en colère. Je me suis éloigné. Je suis allé vers papa. Bravo, Raphaël.</t>
+          <t>Le puzzle est entier. Merci, Raphaël. Le toit rouge reste au milieu. La soupe fume encore, tout doux.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2032,7 +2023,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2104,10 +2095,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|J'ai dit : je suis en colère.
-enfant-m|Je me suis éloigné.
-enfant-m|Je suis allé vers papa.
-papa|Bravo, Raphaël.</t>
+          <t>enfant-m|Le puzzle est entier.
+papa|Merci, Raphaël.
+narrateur|Le toit rouge reste au milieu.
+narrateur|La soupe fume encore, tout doux.</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2178,6 +2169,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
